--- a/design_issues/codescene/P9_LMS.xlsx
+++ b/design_issues/codescene/P9_LMS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\design_issues\codescene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DIinAGP\DIinAGP\design_issues\codescene\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="82">
   <si>
     <t>resource</t>
   </si>
@@ -173,12 +173,6 @@
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/projects/P9_LMS/backend/src/main/java/com/lms/util/JwtUtil.java</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments ()</t>
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/projects/P9_LMS/frontend/src/components/assessment/AssessmentForm.vue</t>
@@ -648,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="121.1796875" customWidth="1"/>
@@ -1765,58 +1759,58 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>214</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D67">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E67">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D68">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E68">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
@@ -1825,15 +1819,15 @@
         <v>23</v>
       </c>
       <c r="D69">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="E69">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
@@ -1842,32 +1836,32 @@
         <v>23</v>
       </c>
       <c r="D70">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="E70">
-        <v>202</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D71">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="E71">
-        <v>61</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B72" t="s">
         <v>8</v>
@@ -1876,32 +1870,32 @@
         <v>9</v>
       </c>
       <c r="D72">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E72">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D73">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="E73">
-        <v>146</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B74" t="s">
         <v>22</v>
@@ -1910,15 +1904,15 @@
         <v>23</v>
       </c>
       <c r="D74">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="E74">
-        <v>112</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
@@ -1927,49 +1921,49 @@
         <v>23</v>
       </c>
       <c r="D75">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="E75">
-        <v>159</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D76">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B78" t="s">
         <v>8</v>
@@ -1978,15 +1972,15 @@
         <v>9</v>
       </c>
       <c r="D78">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E78">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B79" t="s">
         <v>8</v>
@@ -1995,38 +1989,38 @@
         <v>9</v>
       </c>
       <c r="D79">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E79">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C80" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D80">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E80">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D81">
         <v>57</v>
@@ -2037,30 +2031,30 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B82" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C82" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D82">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E82">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D83">
         <v>78</v>
@@ -2071,30 +2065,30 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D84">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E84">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85">
         <v>95</v>
@@ -2105,30 +2099,30 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C86" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D86">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E86">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D87">
         <v>116</v>
@@ -2139,7 +2133,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B88" t="s">
         <v>8</v>
@@ -2148,15 +2142,15 @@
         <v>9</v>
       </c>
       <c r="D88">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="E88">
-        <v>116</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B89" t="s">
         <v>8</v>
@@ -2165,49 +2159,49 @@
         <v>9</v>
       </c>
       <c r="D89">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="E89">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D90">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E90">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D91">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="E91">
-        <v>177</v>
+        <v>195</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B92" t="s">
         <v>8</v>
@@ -2216,66 +2210,66 @@
         <v>9</v>
       </c>
       <c r="D92">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="E92">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B93" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D93">
-        <v>209</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>209</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D95">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E95">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B96" t="s">
         <v>8</v>
@@ -2284,15 +2278,15 @@
         <v>9</v>
       </c>
       <c r="D96">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E96">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B97" t="s">
         <v>8</v>
@@ -2301,49 +2295,49 @@
         <v>9</v>
       </c>
       <c r="D97">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E97">
-        <v>63</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D98">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="E98">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B99" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E99">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B100" t="s">
         <v>8</v>
@@ -2352,15 +2346,15 @@
         <v>9</v>
       </c>
       <c r="D100">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="E100">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B101" t="s">
         <v>8</v>
@@ -2369,49 +2363,49 @@
         <v>9</v>
       </c>
       <c r="D101">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E101">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B102" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D102">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="E102">
-        <v>144</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B103" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B104" t="s">
         <v>8</v>
@@ -2420,15 +2414,15 @@
         <v>9</v>
       </c>
       <c r="D104">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E104">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B105" t="s">
         <v>8</v>
@@ -2437,151 +2431,151 @@
         <v>9</v>
       </c>
       <c r="D105">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E105">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D106">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E106">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B107" t="s">
         <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D107">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E107">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B108" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D108">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E108">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C109" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="D109">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E109">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C110" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D110">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E110">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B111" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D111">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="E111">
-        <v>111</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B112" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D112">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E112">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D113">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="E113">
-        <v>146</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B114" t="s">
         <v>8</v>
@@ -2590,38 +2584,38 @@
         <v>9</v>
       </c>
       <c r="D114">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E114">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B115" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D115">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E115">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
+        <v>59</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
         <v>61</v>
-      </c>
-      <c r="B116" t="s">
-        <v>12</v>
-      </c>
-      <c r="C116" t="s">
-        <v>62</v>
       </c>
       <c r="D116">
         <v>197</v>
@@ -2632,75 +2626,75 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B117" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C117" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D117">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E117">
-        <v>197</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B118" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D118">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="E118">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B119" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C119" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D119">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="E119">
-        <v>258</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B120" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B121" t="s">
         <v>8</v>
@@ -2709,15 +2703,15 @@
         <v>9</v>
       </c>
       <c r="D121">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E121">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B122" t="s">
         <v>8</v>
@@ -2726,38 +2720,38 @@
         <v>9</v>
       </c>
       <c r="D122">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E122">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B123" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D123">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E123">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D124">
         <v>56</v>
@@ -2768,30 +2762,30 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B125" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C125" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D125">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E125">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C126" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D126">
         <v>77</v>
@@ -2802,7 +2796,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B127" t="s">
         <v>8</v>
@@ -2811,15 +2805,15 @@
         <v>9</v>
       </c>
       <c r="D127">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E127">
-        <v>77</v>
+        <v>98</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B128" t="s">
         <v>8</v>
@@ -2828,49 +2822,49 @@
         <v>9</v>
       </c>
       <c r="D128">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E128">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B129" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C129" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D129">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="E129">
-        <v>112</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B130" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B131" t="s">
         <v>8</v>
@@ -2879,15 +2873,15 @@
         <v>9</v>
       </c>
       <c r="D131">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E131">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B132" t="s">
         <v>8</v>
@@ -2896,15 +2890,15 @@
         <v>9</v>
       </c>
       <c r="D132">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E132">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B133" t="s">
         <v>8</v>
@@ -2913,55 +2907,55 @@
         <v>9</v>
       </c>
       <c r="D133">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E133">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B134" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C134" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D134">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="E134">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B135" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E135">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B136" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D136">
         <v>12</v>
@@ -2972,30 +2966,30 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B137" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D137">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E137">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B138" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D138">
         <v>32</v>
@@ -3006,7 +3000,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B139" t="s">
         <v>8</v>
@@ -3015,15 +3009,15 @@
         <v>9</v>
       </c>
       <c r="D139">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E139">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B140" t="s">
         <v>8</v>
@@ -3032,15 +3026,15 @@
         <v>9</v>
       </c>
       <c r="D140">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="E140">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B141" t="s">
         <v>8</v>
@@ -3049,15 +3043,15 @@
         <v>9</v>
       </c>
       <c r="D141">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E141">
-        <v>68</v>
+        <v>83</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B142" t="s">
         <v>8</v>
@@ -3066,15 +3060,15 @@
         <v>9</v>
       </c>
       <c r="D142">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E142">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B143" t="s">
         <v>8</v>
@@ -3083,49 +3077,49 @@
         <v>9</v>
       </c>
       <c r="D143">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="E143">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B144" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C144" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D144">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="E144">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B145" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B146" t="s">
         <v>8</v>
@@ -3134,83 +3128,83 @@
         <v>9</v>
       </c>
       <c r="D146">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E146">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B147" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C147" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D147">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E147">
-        <v>26</v>
+        <v>57</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B148" t="s">
         <v>14</v>
       </c>
       <c r="C148" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D148">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E148">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C149" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D149">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="E149">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B150" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E150">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B151" t="s">
         <v>8</v>
@@ -3219,15 +3213,15 @@
         <v>9</v>
       </c>
       <c r="D151">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E151">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B152" t="s">
         <v>8</v>
@@ -3236,15 +3230,15 @@
         <v>9</v>
       </c>
       <c r="D152">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E152">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B153" t="s">
         <v>8</v>
@@ -3253,15 +3247,15 @@
         <v>9</v>
       </c>
       <c r="D153">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E153">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B154" t="s">
         <v>8</v>
@@ -3270,100 +3264,100 @@
         <v>9</v>
       </c>
       <c r="D154">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E154">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B155" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D155">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E155">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B156" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D156">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E156">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B157" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D157">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="E157">
-        <v>111</v>
+        <v>131</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B158" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C158" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D158">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="E158">
-        <v>131</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B159" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B160" t="s">
         <v>8</v>
@@ -3372,15 +3366,15 @@
         <v>9</v>
       </c>
       <c r="D160">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E160">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B161" t="s">
         <v>8</v>
@@ -3389,15 +3383,15 @@
         <v>9</v>
       </c>
       <c r="D161">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E161">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B162" t="s">
         <v>8</v>
@@ -3406,15 +3400,15 @@
         <v>9</v>
       </c>
       <c r="D162">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E162">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B163" t="s">
         <v>8</v>
@@ -3423,49 +3417,49 @@
         <v>9</v>
       </c>
       <c r="D163">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E163">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B164" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C164" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D164">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="E164">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B165" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B166" t="s">
         <v>8</v>
@@ -3474,15 +3468,15 @@
         <v>9</v>
       </c>
       <c r="D166">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E166">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B167" t="s">
         <v>8</v>
@@ -3491,15 +3485,15 @@
         <v>9</v>
       </c>
       <c r="D167">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E167">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B168" t="s">
         <v>8</v>
@@ -3508,89 +3502,89 @@
         <v>9</v>
       </c>
       <c r="D168">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E168">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
+        <v>68</v>
+      </c>
+      <c r="B169" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169">
         <v>70</v>
       </c>
-      <c r="B169" t="s">
-        <v>8</v>
-      </c>
-      <c r="C169" t="s">
-        <v>9</v>
-      </c>
-      <c r="D169">
-        <v>55</v>
-      </c>
       <c r="E169">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B170" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D170">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E170">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B171" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C171" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D171">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="E171">
-        <v>88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B172" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D172">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E172">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B173" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C173" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D173">
         <v>17</v>
@@ -3601,47 +3595,47 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B174" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D174">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E174">
-        <v>17</v>
+        <v>57</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B175" t="s">
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D175">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E175">
-        <v>57</v>
+        <v>80</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B176" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C176" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D176">
         <v>80</v>
@@ -3652,58 +3646,58 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B177" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D177">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="E177">
-        <v>80</v>
+        <v>264</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B178" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C178" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D178">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="E178">
-        <v>264</v>
+        <v>284</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B179" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D179">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="E179">
-        <v>284</v>
+        <v>334</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B180" t="s">
         <v>8</v>
@@ -3712,15 +3706,15 @@
         <v>9</v>
       </c>
       <c r="D180">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="E180">
-        <v>334</v>
+        <v>348</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B181" t="s">
         <v>8</v>
@@ -3729,32 +3723,32 @@
         <v>9</v>
       </c>
       <c r="D181">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="E181">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B182" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C182" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D182">
-        <v>359</v>
+        <v>304</v>
       </c>
       <c r="E182">
-        <v>359</v>
+        <v>304</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B183" t="s">
         <v>22</v>
@@ -3763,49 +3757,49 @@
         <v>23</v>
       </c>
       <c r="D183">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="E183">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B184" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C184" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D184">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="E184">
-        <v>317</v>
+        <v>352</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B185" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D185">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="E185">
-        <v>352</v>
+        <v>372</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B186" t="s">
         <v>22</v>
@@ -3814,15 +3808,15 @@
         <v>23</v>
       </c>
       <c r="D186">
-        <v>372</v>
+        <v>440</v>
       </c>
       <c r="E186">
-        <v>372</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B187" t="s">
         <v>22</v>
@@ -3831,38 +3825,38 @@
         <v>23</v>
       </c>
       <c r="D187">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="E187">
-        <v>440</v>
+        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B188" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D188">
-        <v>455</v>
+        <v>216</v>
       </c>
       <c r="E188">
-        <v>455</v>
+        <v>216</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B189" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C189" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D189">
         <v>216</v>
@@ -3873,81 +3867,81 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C190" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D190">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="E190">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B191" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C191" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D191">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E191">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B192" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C192" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D192">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="E192">
-        <v>233</v>
+        <v>253</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B193" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C193" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D193">
-        <v>253</v>
+        <v>121</v>
       </c>
       <c r="E193">
-        <v>253</v>
+        <v>121</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B194" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C194" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D194">
         <v>121</v>
@@ -3958,58 +3952,58 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B195" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C195" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D195">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E195">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B196" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C196" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D196">
-        <v>143</v>
+        <v>225</v>
       </c>
       <c r="E196">
-        <v>143</v>
+        <v>225</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B197" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C197" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D197">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="E197">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B198" t="s">
         <v>22</v>
@@ -4018,15 +4012,15 @@
         <v>23</v>
       </c>
       <c r="D198">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="E198">
-        <v>245</v>
+        <v>189</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B199" t="s">
         <v>22</v>
@@ -4035,43 +4029,26 @@
         <v>23</v>
       </c>
       <c r="D199">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="E199">
-        <v>189</v>
+        <v>109</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B200" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C200" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D200">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="E200">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
-        <v>79</v>
-      </c>
-      <c r="B201" t="s">
-        <v>12</v>
-      </c>
-      <c r="C201" t="s">
-        <v>13</v>
-      </c>
-      <c r="D201">
-        <v>145</v>
-      </c>
-      <c r="E201">
         <v>145</v>
       </c>
     </row>
@@ -4082,7 +4059,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D12"/>
+  <dimension ref="A2:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="33.08984375" customWidth="1"/>
@@ -4091,13 +4068,13 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -4109,7 +4086,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIF(Issues!B2:B201,Stats!B3)</f>
+        <f>COUNTIF(Issues!B2:B200,Stats!B3)</f>
         <v>78</v>
       </c>
       <c r="D3" s="2"/>
@@ -4122,7 +4099,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIF(Issues!B2:B202,Stats!B4)</f>
+        <f>COUNTIF(Issues!B2:B201,Stats!B4)</f>
         <v>19</v>
       </c>
       <c r="D4" s="2"/>
@@ -4135,7 +4112,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIF(Issues!B2:B203,Stats!B5)</f>
+        <f>COUNTIF(Issues!B2:B202,Stats!B5)</f>
         <v>52</v>
       </c>
       <c r="D5" s="2"/>
@@ -4148,7 +4125,7 @@
         <v>37</v>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIF(Issues!B2:B204,Stats!B6)</f>
+        <f>COUNTIF(Issues!B2:B203,Stats!B6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="2"/>
@@ -4161,73 +4138,60 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIF(Issues!B2:B205,Stats!B7)</f>
+        <f>COUNTIF(Issues!B2:B204,Stats!B7)</f>
         <v>27</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIF(Issues!B2:B208,Stats!B8)</f>
+        <f>COUNTIF(Issues!B2:B207,Stats!B8)</f>
         <v>5</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIF(Issues!B2:B209,Stats!B9)</f>
+        <f>COUNTIF(Issues!B2:B208,Stats!B9)</f>
         <v>7</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIF(Issues!B2:B210,Stats!B10)</f>
+        <f>COUNTIF(Issues!B2:B209,Stats!B10)</f>
         <v>8</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="2">
-        <f>COUNTIF(Issues!B2:B211,Stats!B11)</f>
-        <v>1</v>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="3">
+        <f>SUM(C3:C10)</f>
+        <v>199</v>
       </c>
       <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="3">
-        <f>SUM(C3:C11)</f>
-        <v>200</v>
-      </c>
-      <c r="D12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
